--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BLENDIO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BLENDIO.xlsx
@@ -565,13 +565,13 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>25.695</v>
+        <v>28.503</v>
       </c>
       <c r="E2" t="n">
-        <v>21.646</v>
+        <v>23.5992</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0491</v>
+        <v>4.904</v>
       </c>
       <c r="G2" t="n">
         <v>35.6751</v>
@@ -610,13 +610,13 @@
         <v>16.5987</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0075</v>
+        <v>0.8006</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.2669</v>
+        <v>-0.3136000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2593000000000001</v>
+        <v>1.1144</v>
       </c>
       <c r="V2" t="n">
         <v>8.626300000000001</v>
@@ -643,13 +643,13 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>6.371600000000001</v>
+        <v>26.4913</v>
       </c>
       <c r="E3" t="n">
-        <v>23.5463</v>
+        <v>36.5498</v>
       </c>
       <c r="F3" t="n">
-        <v>-17.1751</v>
+        <v>-10.0586</v>
       </c>
       <c r="G3" t="n">
         <v>10.0193</v>
@@ -688,13 +688,13 @@
         <v>39.1808</v>
       </c>
       <c r="S3" t="n">
-        <v>-27.758</v>
+        <v>-7.6384</v>
       </c>
       <c r="T3" t="n">
-        <v>-18.5082</v>
+        <v>-5.505</v>
       </c>
       <c r="U3" t="n">
-        <v>-9.2499</v>
+        <v>-2.1335</v>
       </c>
       <c r="V3" t="n">
         <v>47.4644</v>
@@ -721,13 +721,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1676</v>
+        <v>6.9132</v>
       </c>
       <c r="E4" t="n">
-        <v>7.6898</v>
+        <v>8.2065</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.5223</v>
+        <v>-1.2933</v>
       </c>
       <c r="G4" t="n">
         <v>2.4664</v>
@@ -766,13 +766,13 @@
         <v>11.3875</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.8615</v>
+        <v>-1.1157</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4784000000000002</v>
+        <v>0.03830000000000006</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.3831</v>
+        <v>-1.1539</v>
       </c>
       <c r="V4" t="n">
         <v>1.3163</v>
@@ -799,13 +799,13 @@
         <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>0.749200000000001</v>
+        <v>3.3591</v>
       </c>
       <c r="E5" t="n">
-        <v>12.0185</v>
+        <v>10.7235</v>
       </c>
       <c r="F5" t="n">
-        <v>-11.2694</v>
+        <v>-7.364299999999999</v>
       </c>
       <c r="G5" t="n">
         <v>-1.545399999999999</v>
@@ -844,13 +844,13 @@
         <v>33.9693</v>
       </c>
       <c r="S5" t="n">
-        <v>-4.798299999999999</v>
+        <v>-2.1882</v>
       </c>
       <c r="T5" t="n">
-        <v>1.952</v>
+        <v>0.6571000000000002</v>
       </c>
       <c r="U5" t="n">
-        <v>-6.7499</v>
+        <v>-2.8451</v>
       </c>
       <c r="V5" t="n">
         <v>-9.6991</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1514</v>
+        <v>0.1781</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1514</v>
+        <v>0.1781</v>
       </c>
       <c r="G6" t="n">
         <v>0.1335</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.4039</v>
+        <v>-2.5248</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.1065</v>
+        <v>-3.468</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7025999999999999</v>
+        <v>0.9432000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3016</v>
@@ -1000,13 +1000,13 @@
         <v>1.158</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0867</v>
+        <v>-0.2076</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3088</v>
+        <v>-0.6701999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2221</v>
+        <v>0.4627</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2436999999999998</v>
@@ -1033,13 +1033,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.2995</v>
+        <v>-6.1322</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6266</v>
+        <v>-2.7267</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.6729</v>
+        <v>-3.4055</v>
       </c>
       <c r="G8" t="n">
         <v>-3.3016</v>
@@ -1078,13 +1078,13 @@
         <v>0.579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7278</v>
+        <v>-0.5605</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1652</v>
+        <v>-0.2653</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5625</v>
+        <v>-0.2951</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8842</v>
@@ -1111,13 +1111,13 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>-11.3293</v>
+        <v>-10.1709</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.817299999999999</v>
+        <v>-3.7015</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.5119</v>
+        <v>-6.4696</v>
       </c>
       <c r="G9" t="n">
         <v>-4.9667</v>
@@ -1156,13 +1156,13 @@
         <v>6.7551</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.4085</v>
+        <v>-1.2503</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1858</v>
+        <v>-1.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.223</v>
+        <v>-0.1806</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0591</v>
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>-14.0581</v>
+        <v>-11.2413</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.804399999999999</v>
+        <v>-5.4056</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.2536</v>
+        <v>-5.835799999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-6.6519</v>
@@ -1234,13 +1234,13 @@
         <v>4.824999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-7.5617</v>
+        <v>-4.744899999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-4.0478</v>
+        <v>-2.6487</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.514</v>
+        <v>-2.0961</v>
       </c>
       <c r="V10" t="n">
         <v>2.0857</v>
@@ -1267,13 +1267,13 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>-14.9316</v>
+        <v>-13.6034</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.216</v>
+        <v>-4.7967</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.715499999999999</v>
+        <v>-8.806800000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-7.9992</v>
@@ -1312,13 +1312,13 @@
         <v>2.509</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.6465</v>
+        <v>-1.3182</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5102</v>
+        <v>-0.09079999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.1363</v>
+        <v>-1.2275</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7418</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. IBARLUCEA LAVIN</t>
+          <t>G. PEREZ CABRERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>-17.9603</v>
+        <v>-13.6804</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.5854</v>
+        <v>2.7725</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.374699999999999</v>
+        <v>-16.4531</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.1788</v>
+        <v>-3.3394</v>
       </c>
       <c r="H12" t="n">
-        <v>-12.7262</v>
+        <v>-5.1923</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4527000000000001</v>
+        <v>1.8529</v>
       </c>
       <c r="J12" t="n">
-        <v>9.514099999999999</v>
+        <v>16.3723</v>
       </c>
       <c r="K12" t="n">
-        <v>4.0925</v>
+        <v>7.724399999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>5.4219</v>
+        <v>8.6479</v>
       </c>
       <c r="M12" t="n">
-        <v>-22.693</v>
+        <v>-19.7116</v>
       </c>
       <c r="N12" t="n">
-        <v>-16.8184</v>
+        <v>-12.9167</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.874599999999999</v>
+        <v>-6.794700000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>5.597099999999999</v>
+        <v>-6.9484</v>
       </c>
       <c r="Q12" t="n">
-        <v>-20.6518</v>
+        <v>-22.0029</v>
       </c>
       <c r="R12" t="n">
-        <v>26.2491</v>
+        <v>15.0546</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.0641</v>
+        <v>-6.175</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.6887</v>
+        <v>-5.5493</v>
       </c>
       <c r="U12" t="n">
-        <v>1.625</v>
+        <v>-0.6255999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.3149</v>
+        <v>2.7822</v>
       </c>
       <c r="W12" t="n">
-        <v>7.2411</v>
+        <v>13.9526</v>
       </c>
       <c r="X12" t="n">
-        <v>-12.556</v>
+        <v>-11.1706</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H. BARREIRO ESCARCEGA</t>
+          <t>D. MERKVILADZE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.1894</v>
+        <v>-14.4859</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.0345</v>
+        <v>5.807500000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.155099999999999</v>
+        <v>-20.2938</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.4675</v>
+        <v>19.3935</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.3573</v>
+        <v>-1.0884</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.1103</v>
+        <v>20.4817</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3304999999999999</v>
+        <v>52.5173</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1694</v>
+        <v>18.4571</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8389</v>
+        <v>34.0601</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.798</v>
+        <v>-33.1235</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.5266</v>
+        <v>-19.5452</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.2714</v>
+        <v>-13.5783</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.5972</v>
+        <v>-10.4223</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.071199999999999</v>
+        <v>-44.1985</v>
       </c>
       <c r="R13" t="n">
-        <v>3.474</v>
+        <v>33.7768</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.8741</v>
+        <v>-9.299300000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.2937</v>
+        <v>-7.9521</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.5806</v>
+        <v>-1.3469</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.2507</v>
+        <v>-14.1583</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>5.4416</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.2507</v>
+        <v>-19.5997</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. PEREZ CABRERA</t>
+          <t>D. IBARLUCEA LAVIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.6534</v>
+        <v>-15.0098</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.0891</v>
+        <v>-7.230299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.5644</v>
+        <v>-7.7797</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.3394</v>
+        <v>-13.1788</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.1923</v>
+        <v>-12.7262</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8529</v>
+        <v>-0.4527000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>16.3723</v>
+        <v>9.514099999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>7.724399999999999</v>
+        <v>4.0925</v>
       </c>
       <c r="L14" t="n">
-        <v>8.6479</v>
+        <v>5.4219</v>
       </c>
       <c r="M14" t="n">
-        <v>-19.7116</v>
+        <v>-22.693</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.9167</v>
+        <v>-16.8184</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.794700000000001</v>
+        <v>-5.874599999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.9484</v>
+        <v>5.597099999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-22.0029</v>
+        <v>-20.6518</v>
       </c>
       <c r="R14" t="n">
-        <v>15.0546</v>
+        <v>26.2491</v>
       </c>
       <c r="S14" t="n">
-        <v>-14.1478</v>
+        <v>-2.1136</v>
       </c>
       <c r="T14" t="n">
-        <v>-11.4111</v>
+        <v>-3.3334</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.7368</v>
+        <v>1.2198</v>
       </c>
       <c r="V14" t="n">
-        <v>2.7822</v>
+        <v>-5.3149</v>
       </c>
       <c r="W14" t="n">
-        <v>13.9526</v>
+        <v>7.2411</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.1706</v>
+        <v>-12.556</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>H. BARREIRO ESCARCEGA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>-25.0426</v>
+        <v>-16.3346</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.5965</v>
+        <v>-10.1957</v>
       </c>
       <c r="F15" t="n">
-        <v>-10.4458</v>
+        <v>-6.1391</v>
       </c>
       <c r="G15" t="n">
-        <v>-35.14239999999999</v>
+        <v>-5.4675</v>
       </c>
       <c r="H15" t="n">
-        <v>-23.0343</v>
+        <v>-2.3573</v>
       </c>
       <c r="I15" t="n">
-        <v>-12.1082</v>
+        <v>-3.1103</v>
       </c>
       <c r="J15" t="n">
-        <v>17.2731</v>
+        <v>0.3304999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>8.499600000000001</v>
+        <v>1.1694</v>
       </c>
       <c r="L15" t="n">
-        <v>8.7735</v>
+        <v>-0.8389</v>
       </c>
       <c r="M15" t="n">
-        <v>-52.4154</v>
+        <v>-5.798</v>
       </c>
       <c r="N15" t="n">
-        <v>-31.5338</v>
+        <v>-3.5266</v>
       </c>
       <c r="O15" t="n">
-        <v>-20.8813</v>
+        <v>-2.2714</v>
       </c>
       <c r="P15" t="n">
-        <v>-14.4757</v>
+        <v>-5.5972</v>
       </c>
       <c r="Q15" t="n">
-        <v>-62.1483</v>
+        <v>-9.071199999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>47.6735</v>
+        <v>3.474</v>
       </c>
       <c r="S15" t="n">
-        <v>35.9978</v>
+        <v>-3.0194</v>
       </c>
       <c r="T15" t="n">
-        <v>17.49</v>
+        <v>-1.4547</v>
       </c>
       <c r="U15" t="n">
-        <v>18.5081</v>
+        <v>-1.5646</v>
       </c>
       <c r="V15" t="n">
-        <v>-11.4221</v>
+        <v>-2.2507</v>
       </c>
       <c r="W15" t="n">
-        <v>12.7896</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-24.2118</v>
+        <v>-2.2507</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. MERKVILADZE</t>
+          <t>I. VILLAVERDE GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>-27.5294</v>
+        <v>-26.0285</v>
       </c>
       <c r="E16" t="n">
-        <v>1.215999999999999</v>
+        <v>-13.3964</v>
       </c>
       <c r="F16" t="n">
-        <v>-28.7457</v>
+        <v>-12.6322</v>
       </c>
       <c r="G16" t="n">
-        <v>19.3935</v>
+        <v>-6.0801</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0884</v>
+        <v>-3.9087</v>
       </c>
       <c r="I16" t="n">
-        <v>20.4817</v>
+        <v>-2.1713</v>
       </c>
       <c r="J16" t="n">
-        <v>52.5173</v>
+        <v>5.2025</v>
       </c>
       <c r="K16" t="n">
-        <v>18.4571</v>
+        <v>2.9906</v>
       </c>
       <c r="L16" t="n">
-        <v>34.0601</v>
+        <v>2.2122</v>
       </c>
       <c r="M16" t="n">
-        <v>-33.1235</v>
+        <v>-11.2827</v>
       </c>
       <c r="N16" t="n">
-        <v>-19.5452</v>
+        <v>-6.8992</v>
       </c>
       <c r="O16" t="n">
-        <v>-13.5783</v>
+        <v>-4.3834</v>
       </c>
       <c r="P16" t="n">
-        <v>-10.4223</v>
+        <v>-13.7036</v>
       </c>
       <c r="Q16" t="n">
-        <v>-44.1985</v>
+        <v>-21.6168</v>
       </c>
       <c r="R16" t="n">
-        <v>33.7768</v>
+        <v>7.9133</v>
       </c>
       <c r="S16" t="n">
-        <v>-22.3426</v>
+        <v>-3.8733</v>
       </c>
       <c r="T16" t="n">
-        <v>-12.5436</v>
+        <v>-2.1797</v>
       </c>
       <c r="U16" t="n">
-        <v>-9.799200000000001</v>
+        <v>-1.6937</v>
       </c>
       <c r="V16" t="n">
-        <v>-14.1583</v>
+        <v>-2.3714</v>
       </c>
       <c r="W16" t="n">
-        <v>5.4416</v>
+        <v>5.1977</v>
       </c>
       <c r="X16" t="n">
-        <v>-19.5997</v>
+        <v>-7.5693</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. VILLAVERDE GONZALEZ</t>
+          <t>M. MENDEZ MADERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>-28.1396</v>
+        <v>-32.7776</v>
       </c>
       <c r="E17" t="n">
-        <v>-13.2338</v>
+        <v>-20.0347</v>
       </c>
       <c r="F17" t="n">
-        <v>-14.9059</v>
+        <v>-12.7424</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.0801</v>
+        <v>-18.5895</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.9087</v>
+        <v>1.5671</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.1713</v>
+        <v>-20.1567</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2025</v>
+        <v>-3.872700000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9906</v>
+        <v>11.1928</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2122</v>
+        <v>-15.0654</v>
       </c>
       <c r="M17" t="n">
-        <v>-11.2827</v>
+        <v>-14.7168</v>
       </c>
       <c r="N17" t="n">
-        <v>-6.8992</v>
+        <v>-9.625500000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.3834</v>
+        <v>-5.0913</v>
       </c>
       <c r="P17" t="n">
-        <v>-13.7036</v>
+        <v>3.6672</v>
       </c>
       <c r="Q17" t="n">
-        <v>-21.6168</v>
+        <v>-12.1593</v>
       </c>
       <c r="R17" t="n">
-        <v>7.9133</v>
+        <v>15.8263</v>
       </c>
       <c r="S17" t="n">
-        <v>-5.9846</v>
+        <v>-5.6194</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.0171</v>
+        <v>-4.4896</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.9672</v>
+        <v>-1.1296</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.3714</v>
+        <v>-12.2353</v>
       </c>
       <c r="W17" t="n">
-        <v>5.1977</v>
+        <v>0.4874</v>
       </c>
       <c r="X17" t="n">
-        <v>-7.5693</v>
+        <v>-12.7227</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-30.4419</v>
+        <v>-34.8705</v>
       </c>
       <c r="E18" t="n">
-        <v>-8.311999999999999</v>
+        <v>-8.6899</v>
       </c>
       <c r="F18" t="n">
-        <v>-22.1296</v>
+        <v>-26.181</v>
       </c>
       <c r="G18" t="n">
         <v>-16.2209</v>
@@ -1858,13 +1858,13 @@
         <v>43.8129</v>
       </c>
       <c r="S18" t="n">
-        <v>7.016100000000001</v>
+        <v>2.586799999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-5.456</v>
+        <v>-5.8339</v>
       </c>
       <c r="U18" t="n">
-        <v>12.4723</v>
+        <v>8.4209</v>
       </c>
       <c r="V18" t="n">
         <v>22.3836</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MENDEZ MADERA</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-37.8625</v>
+        <v>-51.8754</v>
       </c>
       <c r="E19" t="n">
-        <v>-20.3861</v>
+        <v>-32.3204</v>
       </c>
       <c r="F19" t="n">
-        <v>-17.4764</v>
+        <v>-19.5547</v>
       </c>
       <c r="G19" t="n">
-        <v>-18.5895</v>
+        <v>-35.14239999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5671</v>
+        <v>-23.0343</v>
       </c>
       <c r="I19" t="n">
-        <v>-20.1567</v>
+        <v>-12.1082</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.872700000000001</v>
+        <v>17.2731</v>
       </c>
       <c r="K19" t="n">
-        <v>11.1928</v>
+        <v>8.499600000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-15.0654</v>
+        <v>8.7735</v>
       </c>
       <c r="M19" t="n">
-        <v>-14.7168</v>
+        <v>-52.4154</v>
       </c>
       <c r="N19" t="n">
-        <v>-9.625500000000001</v>
+        <v>-31.5338</v>
       </c>
       <c r="O19" t="n">
-        <v>-5.0913</v>
+        <v>-20.8813</v>
       </c>
       <c r="P19" t="n">
-        <v>3.6672</v>
+        <v>-14.4757</v>
       </c>
       <c r="Q19" t="n">
-        <v>-12.1593</v>
+        <v>-62.1483</v>
       </c>
       <c r="R19" t="n">
-        <v>15.8263</v>
+        <v>47.6735</v>
       </c>
       <c r="S19" t="n">
-        <v>-10.7045</v>
+        <v>9.1648</v>
       </c>
       <c r="T19" t="n">
-        <v>-4.841</v>
+        <v>-0.2342999999999998</v>
       </c>
       <c r="U19" t="n">
-        <v>-5.8641</v>
+        <v>9.398900000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-12.2353</v>
+        <v>-11.4221</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4874</v>
+        <v>12.7896</v>
       </c>
       <c r="X19" t="n">
-        <v>-12.7227</v>
+        <v>-24.2118</v>
       </c>
     </row>
     <row r="20">
@@ -1969,22 +1969,22 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-218.7067</v>
+        <v>-183.2906</v>
       </c>
       <c r="E20" t="n">
-        <v>-37.6916</v>
+        <v>-24.30690000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-181.0152</v>
+        <v>-158.9846</v>
       </c>
       <c r="G20" t="n">
         <v>-56.09719999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-55.96900000000001</v>
+        <v>-55.969</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1288999999999945</v>
+        <v>-0.1288999999999891</v>
       </c>
       <c r="J20" t="n">
         <v>260.5576</v>
@@ -2008,22 +2008,22 @@
         <v>-111.9449</v>
       </c>
       <c r="Q20" t="n">
-        <v>-422.6857999999999</v>
+        <v>-422.6858</v>
       </c>
       <c r="R20" t="n">
         <v>310.7429</v>
       </c>
       <c r="S20" t="n">
-        <v>-71.9425</v>
+        <v>-36.527</v>
       </c>
       <c r="T20" t="n">
-        <v>-54.28050000000001</v>
+        <v>-40.8949</v>
       </c>
       <c r="U20" t="n">
-        <v>-17.662</v>
+        <v>4.369100000000003</v>
       </c>
       <c r="V20" t="n">
-        <v>21.2779</v>
+        <v>21.27790000000001</v>
       </c>
       <c r="W20" t="n">
         <v>178.7208</v>
